--- a/generated/spreadsheet/verbose/advertising-consent-advertising-verbose.xlsx
+++ b/generated/spreadsheet/verbose/advertising-consent-advertising-verbose.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:N98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -440,9 +440,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="72" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2476,19 +2476,27 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>address-text</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>Address Text</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -2532,19 +2540,27 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -2578,21 +2594,37 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>company</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>The name of a company (that the agent works for)</t>
+          <t>Unique Property Reference Number for a property</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -2626,12 +2658,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>user-role</t>
+          <t>company</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>User role</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2640,12 +2672,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>The role of the named individual. Agent or proxy</t>
+          <t>The name of a company (that the agent works for)</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2655,56 +2687,64 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Applicant contact details</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>applicant-contact</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Telephone number and email address of the applicant.</t>
+          <t>Name and contact information if an agent is being used.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>applicant-reference</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Applicant reference</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>user-role</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>User role</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Reference to match contact details to a named individual from the applicant details component</t>
+          <t>The role of the named individual. Agent or proxy</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Applicant contact details</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>applicant-contact</t>
+        </is>
+      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Telephone number and email address of the applicant.</t>
@@ -2712,31 +2752,23 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>contact-details</t>
+          <t>applicant-reference</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Contact details</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
+          <t>Applicant reference</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>The email address that can be used for electronic correspondence with the individual</t>
+          <t>Reference to match contact details to a named individual from the applicant details component</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -2770,29 +2802,21 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>phone-numbers</t>
+          <t>email</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Phone number(s)[]</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -2802,7 +2826,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -2836,24 +2860,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>contact-priority</t>
+          <t>number</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Contact priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>The priority of a number</t>
+          <t>A phone number</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2863,64 +2887,72 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Applicant details</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>applicant-details</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Name and contact information for the parties making the application.</t>
+          <t>Telephone number and email address of the applicant.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>applicants</t>
+          <t>contact-details</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Applicants[]</t>
+          <t>Contact details</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>phone-numbers</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+          <t>Phone number(s)[]</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>contact-priority</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Contact priority</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>The priority of a number</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Applicant details</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>applicant-details</t>
+        </is>
+      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Name and contact information for the parties making the application.</t>
@@ -2938,29 +2970,21 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>The title of the individual</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -2970,7 +2994,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3004,19 +3028,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>first-name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>The first name of the individual</t>
+          <t>The title of the individual</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -3026,7 +3050,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3060,19 +3084,19 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>last-name</t>
+          <t>first-name</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>The last name of the individual</t>
+          <t>The first name of the individual</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -3116,19 +3140,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>last-name</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>The last name of the individual</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -3172,144 +3196,192 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Text representation of an address or site</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>postcode</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>Postcode</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>The postal code</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Postcode for a contact address or site</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Name and contact information for the parties making the application.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>applicants</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Applicants[]</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>contact-address</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Contact address</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>uprn</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>UPRN</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Unique Property Reference Number for a property</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Checklist</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>checklist</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Checking whether all the requirements of the form have been met, such as proof of payment or supporting documentation.</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>national-req-types</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>National requirement types[]</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>List of the document types required for the given application type</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Community consultation</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>community-consultation</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>have-consulted</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Have consulted</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>Whether community consultation has been carried out</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>MUST</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>What community consultation activities have taken place as part of the application</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3320,7 +3392,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Provide details of the community consultation</t>
+          <t>List of the document types required for the given application type</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -3330,34 +3402,34 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Conflict of interest</t>
+          <t>Community consultation</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>conflict-of-interest</t>
+          <t>community-consultation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>conflict-to-declare</t>
+          <t>have-consulted</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Conflict to declare</t>
+          <t>Have consulted</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3368,7 +3440,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
+          <t>Whether community consultation has been carried out</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -3387,17 +3459,17 @@
       <c r="B57" s="2" t="n"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
+          <t>What community consultation activities have taken place as part of the application</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3408,7 +3480,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Reference to the applicant or agent with the conflict</t>
+          <t>Provide details of the community consultation</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -3423,8 +3495,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Conflict of interest</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>conflict-of-interest</t>
+        </is>
+      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
@@ -3432,12 +3512,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>conflict-details</t>
+          <t>conflict-to-declare</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Conflict details</t>
+          <t>Conflict to declare</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3448,44 +3528,36 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
+          <t>Indicates whether any named applicant or agent has a relationship to the planning authority that must be declared</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Interest in land</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>interest-in-land</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>applicant-owns-land</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Applicant owns land</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3496,17 +3568,17 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether the applicant owns the land where the advertisement will be displayed</t>
+          <t>Reference to the applicant or agent with the conflict</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3515,17 +3587,17 @@
       <c r="B60" s="2" t="n"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
+          <t>Details of any conflict of interest that may exist between the applicant and planning authority.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>permission-obtained</t>
+          <t>conflict-details</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Permission obtained</t>
+          <t>Conflict details</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3536,12 +3608,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>True or False indicating whether permission of the owner for the display of an advertisement has been obtained</t>
+          <t>Details of the conflict of interest including name, role and how the individual is related to the planning authority</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -3551,8 +3623,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Interest in land</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>interest-in-land</t>
+        </is>
+      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
@@ -3560,12 +3640,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>permission-not-obtained-details</t>
+          <t>applicant-owns-land</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Permission not obtained details</t>
+          <t>Applicant owns land</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3576,44 +3656,36 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Details explaining why permission from the land owner has not been obtained for the advertisement display</t>
+          <t>True or False indicating whether the applicant owns the land where the advertisement will be displayed</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Declaration</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>declaration</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>person-reference</t>
+          <t>permission-obtained</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Person reference</t>
+          <t>Permission obtained</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3624,17 +3696,17 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Declaration must be made by an applicant or agent making the application</t>
+          <t>True or False indicating whether permission of the owner for the display of an advertisement has been obtained</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -3643,17 +3715,17 @@
       <c r="B63" s="2" t="n"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Signed and dated verification of the application's accuracy.</t>
+          <t>Whether the applicant owns or has permission to use the land where the proposed advertisement will be placed</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>declaration-confirmed</t>
+          <t>permission-not-obtained-details</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Declaration confirmed</t>
+          <t>Permission not obtained details</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3664,23 +3736,31 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
+          <t>Details explaining why permission from the land owner has not been obtained for the advertisement display</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Declaration</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>declaration</t>
+        </is>
+      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Signed and dated verification of the application's accuracy.</t>
@@ -3688,12 +3768,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>declaration-date</t>
+          <t>person-reference</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Declaration date</t>
+          <t>Person reference</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3704,12 +3784,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>The date the declaration was made</t>
+          <t>Declaration must be made by an applicant or agent making the application</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3719,29 +3799,21 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Pre-application advice</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>pre-app-advice</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>advice-sought</t>
+          <t>declaration-confirmed</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Pre-application advice sought</t>
+          <t>Declaration confirmed</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3752,7 +3824,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Whether pre-application advice has been sought from the planning authority</t>
+          <t>Confirms the applicant or agent has reviewed and validated the information provided in the application</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -3771,17 +3843,17 @@
       <c r="B66" s="2" t="n"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Details of pre-application advice previously received from the planning authority</t>
+          <t>Signed and dated verification of the application's accuracy.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>officer-name</t>
+          <t>declaration-date</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Declaration date</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3792,23 +3864,31 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Name of the planning officer who provided the pre-application advice</t>
+          <t>The date the declaration was made</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="2" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Pre-application advice</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>pre-app-advice</t>
+        </is>
+      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Details of pre-application advice previously received from the planning authority</t>
@@ -3816,12 +3896,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>advice-sought</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Pre-application advice sought</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3832,17 +3912,17 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>A unique reference for the data item</t>
+          <t>Whether pre-application advice has been sought from the planning authority</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3936,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>advice-date</t>
+          <t>officer-name</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Advice date</t>
+          <t>Officer name</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3872,12 +3952,12 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
+          <t>Name of the planning officer who provided the pre-application advice</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -3896,12 +3976,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>advice-summary</t>
+          <t>reference</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Advice summary</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3912,7 +3992,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Summary of the pre-application advice received from the planning authority</t>
+          <t>A unique reference for the data item</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -3927,53 +4007,37 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Proposed advert details</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>proposed-advert-details</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Details of the proposed advertisements such as their size and how they are made</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>advertisements</t>
+          <t>advice-date</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Advertisements[]</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>height-from-ground</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Height from ground</t>
-        </is>
-      </c>
+          <t>Advice date</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Height, in metres, from ground to the base of the advertisement</t>
+          <t>Date when pre-application advice was received, in YYYY-MM-DD format</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -3987,41 +4051,33 @@
       <c r="B71" s="2" t="n"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Details of the proposed advertisements such as their size and how they are made</t>
+          <t>Details of pre-application advice previously received from the planning authority</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>advertisements</t>
+          <t>advice-summary</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Advertisements[]</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>height</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Height</t>
-        </is>
-      </c>
+          <t>Advice summary</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Height, in metres, of dimensions of advertisement</t>
+          <t>Summary of the pre-application advice received from the planning authority</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -4031,8 +4087,16 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="2" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Proposed advert details</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>proposed-advert-details</t>
+        </is>
+      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Details of the proposed advertisements such as their size and how they are made</t>
@@ -4050,12 +4114,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>height-from-ground</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Height from ground</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4064,7 +4128,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Width of dimensions of advertisement</t>
+          <t>Height, in metres, from ground to the base of the advertisement</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -4098,12 +4162,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>depth</t>
+          <t>height</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Depth</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4112,7 +4176,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Depth, in metres, of dimensions of advertisement</t>
+          <t>Height, in metres, of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -4146,12 +4210,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>symbol-height-max</t>
+          <t>width</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Symbol height max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4160,7 +4224,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Maximum height, in metres, of any individual letters or symbols</t>
+          <t>Width of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -4194,12 +4258,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>colour</t>
+          <t>depth</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Colour</t>
+          <t>Depth</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4208,12 +4272,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Colour of proposed sign</t>
+          <t>Depth, in metres, of dimensions of advertisement</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -4242,12 +4306,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>symbol-height-max</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Symbol height max</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4256,12 +4320,12 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Materials of proposed sign</t>
+          <t>Maximum height, in metres, of any individual letters or symbols</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4290,12 +4354,12 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>max-projection</t>
+          <t>colour</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Max projection</t>
+          <t>Colour</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4304,12 +4368,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Maximum projection, in metres, of the advertisement from the face of the building</t>
+          <t>Colour of proposed sign</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -4338,12 +4402,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>illuminated</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Illuminated</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4352,12 +4416,12 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Will the sign(s) be illuminated?</t>
+          <t>Materials of proposed sign</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -4386,12 +4450,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>illumination-method</t>
+          <t>max-projection</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Illumination method</t>
+          <t>Max projection</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4400,12 +4464,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Method of illumination for the advertisement</t>
+          <t>Maximum projection, in metres, of the advertisement from the face of the building</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -4434,12 +4498,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>illuminance-level</t>
+          <t>illuminated</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Illuminance level</t>
+          <t>Illuminated</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4448,12 +4512,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Level of illuminance for the advertisement</t>
+          <t>Will the sign(s) be illuminated?</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -4482,12 +4546,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>illumination-type</t>
+          <t>illumination-method</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Illumination type</t>
+          <t>Illumination method</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4496,7 +4560,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Type of illumination (static or intermittent)</t>
+          <t>Method of illumination for the advertisement</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -4511,39 +4575,31 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Site details</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>site-details</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the proposed advertisements such as their size and how they are made</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advertisements</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Advertisements[]</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>site-boundary</t>
+          <t>illuminance-level</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Site boundary</t>
+          <t>Illuminance level</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -4552,12 +4608,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Geometry of the site of the development, typically in GeoJSON format</t>
+          <t>Level of illuminance for the advertisement</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>wkt</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -4571,27 +4627,27 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Where the proposed development will be built.</t>
+          <t>Details of the proposed advertisements such as their size and how they are made</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>site-locations</t>
+          <t>advertisements</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Site locations[]</t>
+          <t>Advertisements[]</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>address-text</t>
+          <t>illumination-type</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Address Text</t>
+          <t>Illumination type</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
@@ -4600,12 +4656,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Flexible field for capturing addresses</t>
+          <t>Type of illumination (static or intermittent)</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -4615,8 +4671,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="2" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Site details</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>site-details</t>
+        </is>
+      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Where the proposed development will be built.</t>
@@ -4634,12 +4698,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Postcode</t>
+          <t>Site boundary</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -4648,17 +4712,17 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>The postal code</t>
+          <t>A polygon or multipolygon boundary</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>multipolygon</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4682,31 +4746,39 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>easting</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Easting</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>address-text</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Address Text</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
+          <t>Text representation of an address or site</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -4730,26 +4802,34 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>northing</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Northing</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>postcode</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
+          <t>Postcode for a contact address or site</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -4778,26 +4858,34 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>uprns</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>UPRNs[]</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Property Reference Numbers (UPRNs) for existing premises within a site boundary</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -4826,26 +4914,34 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>site-address</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>usrns</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>USRNs[]</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
+          <t>Unique Street Reference Numbers (USRNs) associated with the site</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>string</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -4874,12 +4970,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>easting</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Easting</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -4888,12 +4984,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>A text description providing details about the subject.</t>
+          <t>Easting coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -4922,12 +5018,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>uprns</t>
+          <t>northing</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>UPRNs[]</t>
+          <t>Northing</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr"/>
@@ -4936,12 +5032,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Unique Property Reference Numbers (UPRNs) for properties within the site boundary</t>
+          <t>Northing coordinate in British National Grid (EPSG:27700)</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -4951,50 +5047,50 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Site Visit Details</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>site-visit</t>
-        </is>
-      </c>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>can-be-seen-from</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Site seen from public area</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
+          <t>Latitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5003,44 +5099,60 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Information to help the planning authority arrange a site visit</t>
+          <t>Where the proposed development will be built.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>contact-type</t>
+          <t>site-locations</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Site visit contact type</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+          <t>Site locations[]</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Indicates who the authority should contact to arrange a site visit</t>
+          <t>Longitude coordinate in WGS84 (EPSG:4326)</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="2" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Site Visit Details</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>site-visit</t>
+        </is>
+      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Information to help the planning authority arrange a site visit</t>
@@ -5048,12 +5160,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>contact-reference</t>
+          <t>can-be-seen-from</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Contact reference</t>
+          <t>Site seen from public area</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
@@ -5064,17 +5176,17 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>The reference of the applicant or agent who should be contacted for site visits</t>
+          <t>Can site be seen from a public road, public footpath, bridleway or other public land</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>MAY</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
@@ -5088,36 +5200,28 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-type</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>fullname</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Full name</t>
-        </is>
-      </c>
+          <t>Site visit contact type</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>The complete name of a person</t>
+          <t>Indicates who the authority should contact to arrange a site visit</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -5136,31 +5240,23 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>other-contact</t>
+          <t>contact-reference</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Other site visit contact</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Phone number</t>
-        </is>
-      </c>
+          <t>Contact reference</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>A phone number</t>
+          <t>The reference of the applicant or agent who should be contacted for site visits</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -5170,7 +5266,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5290,12 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>fullname</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Full name</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr"/>
@@ -5208,15 +5304,111 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
+          <t>The complete name of a person</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>A phone number</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Information to help the planning authority arrange a site visit</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>other-contact</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Other site visit contact</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
           <t>The email address that can be used for electronic correspondence with the individual</t>
         </is>
       </c>
-      <c r="M96" s="2" t="inlineStr">
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>MUST</t>
         </is>
@@ -5224,40 +5416,40 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A35:A42"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B35:B42"/>
-    <mergeCell ref="A53"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B82:B90"/>
+    <mergeCell ref="B48:B54"/>
+    <mergeCell ref="B55"/>
     <mergeCell ref="A20:A24"/>
     <mergeCell ref="A2:A19"/>
-    <mergeCell ref="A54:A55"/>
     <mergeCell ref="B27:B30"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B47:B52"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B93:B98"/>
+    <mergeCell ref="B84:B92"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A56:A57"/>
     <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B64:B66"/>
     <mergeCell ref="B20:B24"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B72:B83"/>
     <mergeCell ref="A27:A30"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="A70:A81"/>
-    <mergeCell ref="A91:A96"/>
-    <mergeCell ref="A82:A90"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B70:B81"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="A35:A43"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B35:B43"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B67:B71"/>
     <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B53"/>
-    <mergeCell ref="A65:A69"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="B56:B57"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B2:B19"/>
-    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A72:A83"/>
+    <mergeCell ref="A93:A98"/>
+    <mergeCell ref="A84:A92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
